--- a/grupos/3APV - Estadisticos 20221.xlsx
+++ b/grupos/3APV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="131">
   <si>
     <t>Materia</t>
   </si>
@@ -164,21 +164,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Sánchez Sánchez Miguel</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Sánchez Sánchez Miguel</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -215,193 +215,193 @@
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>QUERO</t>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>SAMANTHA MIA</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>MELANY NARAYANA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>CORONADO</t>
+  </si>
+  <si>
+    <t>OCHOA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
   </si>
   <si>
     <t>TLAXCALTECA</t>
   </si>
   <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>MARILYN</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERMIN</t>
   </si>
   <si>
     <t>CLAUDIA</t>
   </si>
   <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>PAUL ADRIAN</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>DANIEL OCTAVIO</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
   </si>
   <si>
     <t>MARIANA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>MELANY NARAYANA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
-  </si>
-  <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>MARILYN</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>DANIEL OCTAVIO</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
   </si>
   <si>
     <t>GABRIELA DENISSE</t>
@@ -908,7 +908,7 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -962,7 +962,7 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>-1</v>
@@ -1370,7 +1370,7 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G10">
         <v>9</v>
@@ -1424,7 +1424,7 @@
         <v>-1</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1678,7 +1678,7 @@
         <v>-1</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -1732,7 +1732,7 @@
         <v>-1</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>-1</v>
@@ -1909,7 +1909,7 @@
         <v>8</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>8</v>
@@ -1963,7 +1963,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2217,7 +2217,7 @@
         <v>6</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -2271,7 +2271,7 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>-1</v>
@@ -2294,7 +2294,7 @@
         <v>-1</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>7</v>
@@ -2348,7 +2348,7 @@
         <v>-1</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2448,7 +2448,7 @@
         <v>7</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G24">
         <v>7</v>
@@ -2502,7 +2502,7 @@
         <v>7</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2660,7 +2660,7 @@
         <v>8</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G28">
         <v>-1</v>
@@ -2714,7 +2714,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>-1</v>
@@ -2737,7 +2737,7 @@
         <v>-1</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G29">
         <v>-1</v>
@@ -2791,7 +2791,7 @@
         <v>-1</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>-1</v>
@@ -2927,16 +2927,16 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>48</v>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -2948,10 +2948,10 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J2">
         <v>50</v>
@@ -2959,13 +2959,13 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>14</v>
@@ -2974,24 +2974,24 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J3">
-        <v>50</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -3000,89 +3000,89 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>53.85</v>
+        <v>65.38</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>46.15</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
       </c>
       <c r="C5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>65.38</v>
+        <v>67.86</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5">
         <v>9</v>
       </c>
       <c r="J5">
-        <v>34.62</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>67.86</v>
+        <v>84.62</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>32.14</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3124,7 +3124,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3159,33 +3159,33 @@
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920111</v>
+        <v>21330051920112</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>50</v>
@@ -3199,16 +3199,16 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3219,16 +3219,16 @@
         <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3239,16 +3239,16 @@
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3259,36 +3259,36 @@
         <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920112</v>
+        <v>21330051920113</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3299,13 +3299,13 @@
         <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>51</v>
@@ -3319,36 +3319,36 @@
         <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920113</v>
+        <v>21330051920115</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3359,16 +3359,16 @@
         <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3379,16 +3379,16 @@
         <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3399,16 +3399,16 @@
         <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3419,36 +3419,36 @@
         <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920115</v>
+        <v>21330051920117</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
         <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -3459,53 +3459,53 @@
         <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920117</v>
+        <v>21330051920119</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
         <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920117</v>
+        <v>21330051920119</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C19" t="s">
         <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
         <v>49</v>
@@ -3519,13 +3519,13 @@
         <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
         <v>51</v>
@@ -3539,21 +3539,21 @@
         <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920119</v>
+        <v>21330051920120</v>
       </c>
       <c r="B22" t="s">
         <v>63</v>
@@ -3562,18 +3562,18 @@
         <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920119</v>
+        <v>21330051920120</v>
       </c>
       <c r="B23" t="s">
         <v>63</v>
@@ -3582,10 +3582,10 @@
         <v>78</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
         <v>49</v>
@@ -3599,13 +3599,13 @@
         <v>63</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
         <v>51</v>
@@ -3619,13 +3619,13 @@
         <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
         <v>48</v>
@@ -3633,19 +3633,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920120</v>
+        <v>21330051920391</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
         <v>79</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
         <v>50</v>
@@ -3653,19 +3653,19 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920120</v>
+        <v>21330051920391</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
         <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
         <v>52</v>
@@ -3673,19 +3673,19 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920120</v>
+        <v>21330051920391</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
         <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
         <v>49</v>
@@ -3699,13 +3699,13 @@
         <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
         <v>51</v>
@@ -3719,13 +3719,13 @@
         <v>64</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
         <v>48</v>
@@ -3733,87 +3733,87 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920391</v>
+        <v>21330051920125</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s">
         <v>80</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920391</v>
+        <v>21330051920125</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C32" t="s">
         <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E32" t="s">
         <v>6</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920391</v>
+        <v>21330051920125</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
         <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E33" t="s">
         <v>5</v>
       </c>
       <c r="F33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920122</v>
+        <v>21330051920126</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C34" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920125</v>
+        <v>21330051920126</v>
       </c>
       <c r="B35" t="s">
         <v>66</v>
@@ -3822,18 +3822,18 @@
         <v>81</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920125</v>
+        <v>21330051920126</v>
       </c>
       <c r="B36" t="s">
         <v>66</v>
@@ -3842,30 +3842,30 @@
         <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F36" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920125</v>
+        <v>21330051920127</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E37" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
         <v>49</v>
@@ -3873,7 +3873,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920126</v>
+        <v>21330051920127</v>
       </c>
       <c r="B38" t="s">
         <v>67</v>
@@ -3882,18 +3882,18 @@
         <v>82</v>
       </c>
       <c r="D38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920126</v>
+        <v>21330051920127</v>
       </c>
       <c r="B39" t="s">
         <v>67</v>
@@ -3902,38 +3902,38 @@
         <v>82</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F39" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>21330051920126</v>
+        <v>21330051920130</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E40" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920127</v>
+        <v>21330051920130</v>
       </c>
       <c r="B41" t="s">
         <v>68</v>
@@ -3942,10 +3942,10 @@
         <v>83</v>
       </c>
       <c r="D41" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F41" t="s">
         <v>48</v>
@@ -3953,99 +3953,99 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920127</v>
+        <v>20330051920152</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C42" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="D42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920127</v>
+        <v>20330051920152</v>
       </c>
       <c r="B43" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C43" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="D43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F43" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920127</v>
+        <v>21330051920133</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D44" t="s">
         <v>99</v>
       </c>
       <c r="E44" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920130</v>
+        <v>21330051920133</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C45" t="s">
         <v>84</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E45" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>21330051920130</v>
+        <v>21330051920133</v>
       </c>
       <c r="B46" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C46" t="s">
         <v>84</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E46" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F46" t="s">
         <v>48</v>
@@ -4053,242 +4053,62 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>21330051920130</v>
+        <v>21330051920134</v>
       </c>
       <c r="B47" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C47" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D47" t="s">
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>18330051920377</v>
+        <v>21330051920134</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C48" t="s">
         <v>85</v>
       </c>
       <c r="D48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E48" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>20330051920152</v>
+        <v>21330051920134</v>
       </c>
       <c r="B49" t="s">
         <v>71</v>
       </c>
       <c r="C49" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="D49" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E49" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F49" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920152</v>
-      </c>
-      <c r="B50" t="s">
-        <v>71</v>
-      </c>
-      <c r="C50" t="s">
-        <v>59</v>
-      </c>
-      <c r="D50" t="s">
-        <v>102</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920152</v>
-      </c>
-      <c r="B51" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" t="s">
-        <v>59</v>
-      </c>
-      <c r="D51" t="s">
-        <v>102</v>
-      </c>
-      <c r="E51" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920133</v>
-      </c>
-      <c r="B52" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" t="s">
-        <v>86</v>
-      </c>
-      <c r="D52" t="s">
-        <v>103</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920133</v>
-      </c>
-      <c r="B53" t="s">
-        <v>72</v>
-      </c>
-      <c r="C53" t="s">
-        <v>86</v>
-      </c>
-      <c r="D53" t="s">
-        <v>103</v>
-      </c>
-      <c r="E53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920133</v>
-      </c>
-      <c r="B54" t="s">
-        <v>72</v>
-      </c>
-      <c r="C54" t="s">
-        <v>86</v>
-      </c>
-      <c r="D54" t="s">
-        <v>103</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920133</v>
-      </c>
-      <c r="B55" t="s">
-        <v>72</v>
-      </c>
-      <c r="C55" t="s">
-        <v>86</v>
-      </c>
-      <c r="D55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920134</v>
-      </c>
-      <c r="B56" t="s">
-        <v>73</v>
-      </c>
-      <c r="C56" t="s">
-        <v>87</v>
-      </c>
-      <c r="D56" t="s">
-        <v>104</v>
-      </c>
-      <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920134</v>
-      </c>
-      <c r="B57" t="s">
-        <v>73</v>
-      </c>
-      <c r="C57" t="s">
-        <v>87</v>
-      </c>
-      <c r="D57" t="s">
-        <v>104</v>
-      </c>
-      <c r="E57" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920134</v>
-      </c>
-      <c r="B58" t="s">
-        <v>73</v>
-      </c>
-      <c r="C58" t="s">
-        <v>87</v>
-      </c>
-      <c r="D58" t="s">
-        <v>104</v>
-      </c>
-      <c r="E58" t="s">
-        <v>5</v>
-      </c>
-      <c r="F58" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -4330,10 +4150,10 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -4347,10 +4167,10 @@
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -4358,16 +4178,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920120</v>
+        <v>21330051920391</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
         <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -4375,24 +4195,24 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920391</v>
+        <v>21330051920119</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920119</v>
+        <v>21330051920120</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -4401,7 +4221,7 @@
         <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -4409,50 +4229,50 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920127</v>
+        <v>21330051920113</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920133</v>
+        <v>21330051920125</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920113</v>
+        <v>21330051920126</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -4460,16 +4280,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920117</v>
+        <v>21330051920127</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -4477,16 +4297,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920125</v>
+        <v>21330051920133</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -4494,16 +4314,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920126</v>
+        <v>21330051920134</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -4511,53 +4331,53 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920130</v>
+        <v>21330051920117</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920152</v>
+        <v>21330051920130</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920134</v>
+        <v>20330051920152</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4568,61 +4388,61 @@
         <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920122</v>
+        <v>21330051920114</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>18330051920377</v>
+        <v>21330051920116</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920114</v>
+        <v>21330051920118</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4630,16 +4450,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920116</v>
+        <v>20330051920266</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4647,16 +4467,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920118</v>
+        <v>21330051920121</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4664,13 +4484,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920266</v>
+        <v>21330051920122</v>
       </c>
       <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
         <v>63</v>
-      </c>
-      <c r="C22" t="s">
-        <v>114</v>
       </c>
       <c r="D22" t="s">
         <v>123</v>
@@ -4681,13 +4501,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920121</v>
+        <v>21330051920123</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
         <v>124</v>
@@ -4698,13 +4518,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920123</v>
-      </c>
-      <c r="B24" t="s">
-        <v>107</v>
+        <v>21330051920129</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
         <v>125</v>
@@ -4715,10 +4532,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920129</v>
+        <v>21330051920131</v>
+      </c>
+      <c r="B25" t="s">
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
         <v>126</v>
@@ -4729,13 +4549,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920131</v>
+        <v>18330051920377</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
         <v>127</v>
@@ -4749,10 +4569,10 @@
         <v>21330051920132</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
         <v>128</v>
@@ -4766,10 +4586,10 @@
         <v>19330051920241</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
         <v>129</v>
@@ -4783,10 +4603,10 @@
         <v>19330051920243</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
         <v>130</v>
@@ -4802,7 +4622,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4834,19 +4654,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920111</v>
+        <v>21330051920117</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>48</v>
@@ -4857,19 +4677,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920111</v>
+        <v>21330051920117</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>50</v>
@@ -4880,19 +4700,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920122</v>
+        <v>21330051920130</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>48</v>
@@ -4903,24 +4723,93 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>18330051920377</v>
+        <v>21330051920130</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920152</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
         <v>48</v>
       </c>
-      <c r="G5">
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920152</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920111</v>
+      </c>
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3APV - Estadisticos 20221.xlsx
+++ b/grupos/3APV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="131">
   <si>
     <t>Materia</t>
   </si>
@@ -164,21 +164,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Sánchez Sánchez Miguel</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Sánchez Sánchez Miguel</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -206,196 +206,196 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>SAMANTHA MIA</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>MELANY NARAYANA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
     <t>ENCARNACION</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MONT</t>
+    <t>LIBRADO</t>
   </si>
   <si>
     <t>QUERO</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
   </si>
   <si>
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>CORONADO</t>
+  </si>
+  <si>
+    <t>OCHOA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>MARILYN</t>
   </si>
   <si>
     <t>DIANA IRAIS</t>
   </si>
   <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>PAUL ADRIAN</t>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERMIN</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>DANIEL OCTAVIO</t>
   </si>
   <si>
     <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>MELANY NARAYANA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
-  </si>
-  <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>MARILYN</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>DANIEL OCTAVIO</t>
   </si>
   <si>
     <t>FATIMA</t>
@@ -914,16 +914,16 @@
         <v>-1</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -950,13 +950,13 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -973,7 +973,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>-1</v>
@@ -982,7 +982,7 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -991,16 +991,16 @@
         <v>-1</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1027,7 +1027,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1036,7 +1036,7 @@
         <v>6</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>-1</v>
@@ -1068,22 +1068,22 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1104,13 +1104,13 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>9</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1119,7 +1119,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1127,7 +1127,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>-1</v>
@@ -1136,7 +1136,7 @@
         <v>6</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1145,22 +1145,22 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1181,22 +1181,22 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1204,7 +1204,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>-1</v>
@@ -1213,7 +1213,7 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -1222,16 +1222,16 @@
         <v>-1</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1258,7 +1258,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1267,7 +1267,7 @@
         <v>5</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>-1</v>
@@ -1299,22 +1299,22 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1358,7 +1358,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <v>7</v>
@@ -1367,7 +1367,7 @@
         <v>7</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -1376,22 +1376,22 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1412,16 +1412,16 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>7</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1453,22 +1453,22 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1489,7 +1489,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -1504,7 +1504,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1512,7 +1512,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C12">
         <v>-1</v>
@@ -1521,7 +1521,7 @@
         <v>5</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>6</v>
@@ -1530,16 +1530,16 @@
         <v>-1</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1566,16 +1566,16 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1607,22 +1607,22 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1643,10 +1643,10 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1658,7 +1658,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1666,7 +1666,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>-1</v>
@@ -1675,7 +1675,7 @@
         <v>7</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>6</v>
@@ -1684,16 +1684,16 @@
         <v>-1</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1720,16 +1720,16 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1761,22 +1761,22 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1800,13 +1800,13 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V15">
         <v>10</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1820,7 +1820,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C16">
         <v>-1</v>
@@ -1829,7 +1829,7 @@
         <v>5</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -1838,16 +1838,16 @@
         <v>-1</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1874,16 +1874,16 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>-1</v>
@@ -1915,22 +1915,22 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1954,19 +1954,19 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1992,22 +1992,22 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2043,7 +2043,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2051,7 +2051,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>-1</v>
@@ -2069,16 +2069,16 @@
         <v>-1</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2105,16 +2105,16 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2128,7 +2128,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <v>-1</v>
@@ -2146,16 +2146,16 @@
         <v>-1</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2182,16 +2182,16 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2205,7 +2205,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>-1</v>
@@ -2223,16 +2223,16 @@
         <v>-1</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2259,16 +2259,16 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2282,7 +2282,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>9</v>
@@ -2291,7 +2291,7 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>6</v>
@@ -2300,22 +2300,22 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2336,16 +2336,16 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>9</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2377,22 +2377,22 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2413,10 +2413,10 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2454,22 +2454,22 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2499,13 +2499,13 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2531,22 +2531,22 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2576,7 +2576,7 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>9</v>
@@ -2596,10 +2596,10 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2608,7 +2608,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>8</v>
@@ -2625,10 +2625,10 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>9</v>
@@ -2648,7 +2648,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C28">
         <v>9</v>
@@ -2666,16 +2666,16 @@
         <v>-1</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2702,16 +2702,16 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>7</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -2725,7 +2725,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>8</v>
@@ -2734,7 +2734,7 @@
         <v>8</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F29">
         <v>6</v>
@@ -2743,16 +2743,16 @@
         <v>-1</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -2779,16 +2779,16 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>8</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>6</v>
@@ -2802,7 +2802,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>8</v>
@@ -2820,16 +2820,16 @@
         <v>-1</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -2856,16 +2856,16 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>-1</v>
@@ -2927,13 +2927,13 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>48</v>
       </c>
       <c r="C2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>14</v>
@@ -2942,51 +2942,51 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
       </c>
       <c r="C3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>53.85</v>
+        <v>67.86</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>46.15</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3000,89 +3000,89 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>69.23</v>
+      </c>
+      <c r="G4">
+        <v>30.77</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>65.38</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>8.1</v>
-      </c>
-      <c r="I4">
-        <v>9</v>
-      </c>
-      <c r="J4">
-        <v>34.62</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>67.86</v>
+        <v>84.62</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>32.14</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="C6">
+        <v>28</v>
+      </c>
+      <c r="D6">
         <v>26</v>
       </c>
-      <c r="D6">
-        <v>22</v>
-      </c>
       <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>92.86</v>
+      </c>
+      <c r="G6">
+        <v>7.14</v>
+      </c>
+      <c r="H6">
+        <v>7.7</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>84.62</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>15.38</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3096,19 +3096,19 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>84.62</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="G7">
-        <v>15.38</v>
+        <v>3.85</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3124,7 +3124,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3159,16 +3159,16 @@
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3179,16 +3179,16 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3199,16 +3199,16 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3219,13 +3219,13 @@
         <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
         <v>49</v>
@@ -3233,99 +3233,99 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920112</v>
+        <v>21330051920113</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920112</v>
+        <v>21330051920115</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
         <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920113</v>
+        <v>21330051920115</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920113</v>
+        <v>21330051920115</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920113</v>
+        <v>21330051920119</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
         <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>48</v>
@@ -3333,59 +3333,59 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920115</v>
+        <v>21330051920119</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920115</v>
+        <v>21330051920120</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
         <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920115</v>
+        <v>21330051920120</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
         <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>49</v>
@@ -3393,19 +3393,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920115</v>
+        <v>21330051920391</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
         <v>51</v>
@@ -3413,19 +3413,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920115</v>
+        <v>21330051920391</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
         <v>48</v>
@@ -3433,39 +3433,39 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920117</v>
+        <v>21330051920391</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
         <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920117</v>
+        <v>21330051920125</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>48</v>
@@ -3473,79 +3473,79 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920119</v>
+        <v>21330051920125</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
         <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920119</v>
+        <v>21330051920126</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920119</v>
+        <v>21330051920126</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920119</v>
+        <v>21330051920127</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
         <v>91</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
         <v>48</v>
@@ -3553,33 +3553,33 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920120</v>
+        <v>21330051920127</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920120</v>
+        <v>20330051920152</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s">
         <v>92</v>
@@ -3588,526 +3588,66 @@
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920120</v>
+        <v>21330051920133</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920120</v>
+        <v>21330051920134</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920391</v>
+        <v>21330051920134</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920391</v>
-      </c>
-      <c r="B27" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920391</v>
-      </c>
-      <c r="B28" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920391</v>
-      </c>
-      <c r="B29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" t="s">
-        <v>93</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920391</v>
-      </c>
-      <c r="B30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" t="s">
-        <v>79</v>
-      </c>
-      <c r="D30" t="s">
-        <v>93</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920125</v>
-      </c>
-      <c r="B31" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" t="s">
-        <v>94</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920125</v>
-      </c>
-      <c r="B32" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" t="s">
-        <v>94</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920125</v>
-      </c>
-      <c r="B33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920126</v>
-      </c>
-      <c r="B34" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920126</v>
-      </c>
-      <c r="B35" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" t="s">
-        <v>95</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920126</v>
-      </c>
-      <c r="B36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" t="s">
-        <v>95</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920127</v>
-      </c>
-      <c r="B37" t="s">
-        <v>67</v>
-      </c>
-      <c r="C37" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920127</v>
-      </c>
-      <c r="B38" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" t="s">
-        <v>82</v>
-      </c>
-      <c r="D38" t="s">
-        <v>96</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920127</v>
-      </c>
-      <c r="B39" t="s">
-        <v>67</v>
-      </c>
-      <c r="C39" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" t="s">
-        <v>96</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920130</v>
-      </c>
-      <c r="B40" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" t="s">
-        <v>97</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920130</v>
-      </c>
-      <c r="B41" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" t="s">
-        <v>83</v>
-      </c>
-      <c r="D41" t="s">
-        <v>97</v>
-      </c>
-      <c r="E41" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920152</v>
-      </c>
-      <c r="B42" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" t="s">
-        <v>59</v>
-      </c>
-      <c r="D42" t="s">
-        <v>98</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920152</v>
-      </c>
-      <c r="B43" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" t="s">
-        <v>59</v>
-      </c>
-      <c r="D43" t="s">
-        <v>98</v>
-      </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920133</v>
-      </c>
-      <c r="B44" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" t="s">
-        <v>84</v>
-      </c>
-      <c r="D44" t="s">
-        <v>99</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920133</v>
-      </c>
-      <c r="B45" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" t="s">
-        <v>84</v>
-      </c>
-      <c r="D45" t="s">
-        <v>99</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920133</v>
-      </c>
-      <c r="B46" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46" t="s">
-        <v>84</v>
-      </c>
-      <c r="D46" t="s">
-        <v>99</v>
-      </c>
-      <c r="E46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920134</v>
-      </c>
-      <c r="B47" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" t="s">
-        <v>85</v>
-      </c>
-      <c r="D47" t="s">
-        <v>100</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920134</v>
-      </c>
-      <c r="B48" t="s">
-        <v>71</v>
-      </c>
-      <c r="C48" t="s">
-        <v>85</v>
-      </c>
-      <c r="D48" t="s">
-        <v>100</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920134</v>
-      </c>
-      <c r="B49" t="s">
-        <v>71</v>
-      </c>
-      <c r="C49" t="s">
-        <v>85</v>
-      </c>
-      <c r="D49" t="s">
-        <v>100</v>
-      </c>
-      <c r="E49" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4150,13 +3690,13 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4167,13 +3707,13 @@
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4181,16 +3721,16 @@
         <v>21330051920391</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4198,16 +3738,16 @@
         <v>21330051920119</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4215,197 +3755,197 @@
         <v>21330051920120</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920113</v>
+        <v>21330051920125</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920125</v>
+        <v>21330051920126</v>
       </c>
       <c r="B8" t="s">
         <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920126</v>
+        <v>21330051920127</v>
       </c>
       <c r="B9" t="s">
         <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920127</v>
+        <v>21330051920134</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920133</v>
+        <v>21330051920111</v>
       </c>
       <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
         <v>70</v>
       </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920134</v>
+        <v>21330051920113</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920117</v>
+        <v>20330051920152</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920130</v>
+        <v>21330051920133</v>
       </c>
       <c r="B14" t="s">
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920152</v>
+        <v>21330051920114</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920111</v>
+        <v>21330051920116</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920114</v>
+        <v>21330051920117</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
         <v>119</v>
@@ -4416,16 +3956,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920116</v>
+        <v>21330051920118</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4433,16 +3973,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920118</v>
+        <v>20330051920266</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4450,13 +3990,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920266</v>
+        <v>21330051920121</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
         <v>121</v>
@@ -4467,13 +4007,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920121</v>
+        <v>21330051920122</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
         <v>122</v>
@@ -4484,13 +4024,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920122</v>
+        <v>21330051920123</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
         <v>123</v>
@@ -4501,13 +4041,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920123</v>
-      </c>
-      <c r="B23" t="s">
-        <v>103</v>
+        <v>21330051920129</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
         <v>124</v>
@@ -4518,10 +4055,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920129</v>
+        <v>21330051920130</v>
+      </c>
+      <c r="B24" t="s">
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
         <v>125</v>
@@ -4535,10 +4075,10 @@
         <v>21330051920131</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
         <v>126</v>
@@ -4552,10 +4092,10 @@
         <v>18330051920377</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
         <v>127</v>
@@ -4569,10 +4109,10 @@
         <v>21330051920132</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
         <v>128</v>
@@ -4586,10 +4126,10 @@
         <v>19330051920241</v>
       </c>
       <c r="B28" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
         <v>129</v>
@@ -4603,10 +4143,10 @@
         <v>19330051920243</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
         <v>130</v>
@@ -4622,7 +4162,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4654,22 +4194,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920117</v>
+        <v>21330051920113</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -4677,16 +4217,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920117</v>
+        <v>21330051920113</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4695,27 +4235,27 @@
         <v>50</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920130</v>
+        <v>21330051920119</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -4723,22 +4263,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920130</v>
+        <v>21330051920119</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -4746,22 +4286,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920152</v>
+        <v>21330051920125</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -4769,22 +4309,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920152</v>
+        <v>21330051920125</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -4792,24 +4332,162 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920111</v>
+        <v>21330051920126</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>49</v>
       </c>
       <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920126</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920133</v>
+      </c>
+      <c r="B10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920133</v>
+      </c>
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920111</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920117</v>
+      </c>
+      <c r="B13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920152</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3APV - Estadisticos 20221.xlsx
+++ b/grupos/3APV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="131">
   <si>
     <t>Materia</t>
   </si>
@@ -167,13 +167,13 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
     <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
@@ -926,7 +926,7 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1080,7 +1080,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -1116,7 +1116,7 @@
         <v>6</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1157,7 +1157,7 @@
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -1311,7 +1311,7 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -1388,7 +1388,7 @@
         <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1424,7 +1424,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1465,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1542,7 +1542,7 @@
         <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1619,7 +1619,7 @@
         <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>9</v>
@@ -1655,7 +1655,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1696,7 +1696,7 @@
         <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1732,7 +1732,7 @@
         <v>5</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>-1</v>
@@ -1773,7 +1773,7 @@
         <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
         <v>10</v>
@@ -1927,7 +1927,7 @@
         <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>10</v>
@@ -1963,7 +1963,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -2004,7 +2004,7 @@
         <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -2040,7 +2040,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2081,7 +2081,7 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2117,7 +2117,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>-1</v>
@@ -2158,7 +2158,7 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2194,7 +2194,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>-1</v>
@@ -2235,7 +2235,7 @@
         <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2271,7 +2271,7 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>-1</v>
@@ -2312,7 +2312,7 @@
         <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>6</v>
@@ -2348,7 +2348,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2389,7 +2389,7 @@
         <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -2425,7 +2425,7 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>10</v>
@@ -2466,7 +2466,7 @@
         <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -2502,7 +2502,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2543,7 +2543,7 @@
         <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>10</v>
@@ -2579,7 +2579,7 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2678,7 +2678,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2755,7 +2755,7 @@
         <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2791,7 +2791,7 @@
         <v>5</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y29">
         <v>-1</v>
@@ -2959,71 +2959,71 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>67.86</v>
+        <v>61.54</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>23.08</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>32.14</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
       </c>
       <c r="C4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>69.23</v>
+        <v>67.86</v>
       </c>
       <c r="G4">
-        <v>30.77</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -3032,25 +3032,25 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>69.23</v>
+      </c>
+      <c r="G5">
+        <v>30.77</v>
+      </c>
+      <c r="H5">
+        <v>6.8</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>84.62</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>15.38</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3188,7 +3188,7 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3228,7 +3228,7 @@
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3248,7 +3248,7 @@
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3268,7 +3268,7 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3308,7 +3308,7 @@
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3348,7 +3348,7 @@
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3388,7 +3388,7 @@
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3408,7 +3408,7 @@
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3448,7 +3448,7 @@
         <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -3488,7 +3488,7 @@
         <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -3528,7 +3528,7 @@
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3568,7 +3568,7 @@
         <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -3628,7 +3628,7 @@
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4162,7 +4162,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4209,7 +4209,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -4232,7 +4232,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4240,68 +4240,68 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920119</v>
+        <v>21330051920117</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920119</v>
+        <v>21330051920117</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920125</v>
+        <v>21330051920119</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -4309,16 +4309,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920125</v>
+        <v>21330051920119</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4332,22 +4332,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920126</v>
+        <v>21330051920125</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -4355,16 +4355,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920126</v>
+        <v>21330051920125</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4378,39 +4378,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920133</v>
+        <v>21330051920126</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>50</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920133</v>
+        <v>21330051920126</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920117</v>
+        <v>21330051920130</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4470,24 +4470,47 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
+        <v>18330051920377</v>
+      </c>
+      <c r="B14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
         <v>20330051920152</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>67</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>59</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>92</v>
       </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
         <v>48</v>
       </c>
-      <c r="G14">
+      <c r="G15">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3APV - Estadisticos 20221.xlsx
+++ b/grupos/3APV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="131">
   <si>
     <t>Materia</t>
   </si>
@@ -985,7 +985,7 @@
         <v>5</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -1003,7 +1003,7 @@
         <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1039,7 +1039,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>-1</v>
@@ -1216,7 +1216,7 @@
         <v>5</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -1234,7 +1234,7 @@
         <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1270,7 +1270,7 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>-1</v>
@@ -1832,7 +1832,7 @@
         <v>5</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -1850,7 +1850,7 @@
         <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1886,7 +1886,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>-1</v>
@@ -2814,7 +2814,7 @@
         <v>7</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G30">
         <v>-1</v>
@@ -2832,7 +2832,7 @@
         <v>5</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -2868,7 +2868,7 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y30">
         <v>-1</v>
@@ -2971,22 +2971,22 @@
         <v>16</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>61.54</v>
       </c>
       <c r="G3">
-        <v>23.08</v>
+        <v>38.46</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3124,7 +3124,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3185,10 +3185,10 @@
         <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3205,24 +3205,24 @@
         <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920112</v>
+        <v>21330051920113</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -3233,22 +3233,22 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920113</v>
+        <v>21330051920115</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3265,24 +3265,24 @@
         <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920115</v>
+        <v>21330051920119</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -3293,16 +3293,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920115</v>
+        <v>21330051920119</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -3313,16 +3313,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920119</v>
+        <v>21330051920120</v>
       </c>
       <c r="B10" t="s">
         <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -3333,16 +3333,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920119</v>
+        <v>21330051920120</v>
       </c>
       <c r="B11" t="s">
         <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -3353,16 +3353,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920120</v>
+        <v>21330051920391</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -3373,16 +3373,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920120</v>
+        <v>21330051920391</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -3393,156 +3393,156 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920391</v>
+        <v>21330051920125</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920391</v>
+        <v>21330051920125</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920391</v>
+        <v>21330051920126</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920125</v>
+        <v>21330051920126</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920125</v>
+        <v>21330051920127</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920126</v>
+        <v>21330051920127</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920126</v>
+        <v>20330051920152</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920127</v>
+        <v>21330051920133</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -3553,101 +3553,21 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920127</v>
+        <v>21330051920134</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920152</v>
-      </c>
-      <c r="B23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920133</v>
-      </c>
-      <c r="B24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920134</v>
-      </c>
-      <c r="B25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" t="s">
-        <v>94</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920134</v>
-      </c>
-      <c r="B26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3696,7 +3616,7 @@
         <v>83</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3713,38 +3633,38 @@
         <v>85</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920391</v>
+        <v>21330051920119</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920119</v>
+        <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -3752,16 +3672,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920120</v>
+        <v>21330051920391</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -3820,33 +3740,33 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920134</v>
+        <v>21330051920111</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920111</v>
+        <v>21330051920113</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -3854,16 +3774,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920113</v>
+        <v>20330051920152</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3871,16 +3791,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920152</v>
+        <v>21330051920133</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -3888,16 +3808,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920133</v>
+        <v>21330051920134</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E14">
         <v>1</v>

--- a/grupos/3APV - Estadisticos 20221.xlsx
+++ b/grupos/3APV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="131">
   <si>
     <t>Materia</t>
   </si>
@@ -164,24 +164,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
   </si>
   <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -203,15 +203,33 @@
     <t>CERVANTES</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -221,6 +239,24 @@
     <t>MONT</t>
   </si>
   <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
@@ -236,22 +272,34 @@
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>GARNICA</t>
   </si>
   <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>CAPORAL</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>CORONADO</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
@@ -260,6 +308,24 @@
     <t>BRAVO</t>
   </si>
   <si>
+    <t>OCHOA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>MONTIEL</t>
   </si>
   <si>
@@ -275,18 +341,39 @@
     <t>SAMANTHA MIA</t>
   </si>
   <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
     <t>DIEGO DE JESUS</t>
   </si>
   <si>
+    <t>MARILYN</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
     <t>GAEL</t>
   </si>
   <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
     <t>NATALIE</t>
   </si>
   <si>
+    <t>CRISTIAN FERMIN</t>
+  </si>
+  <si>
     <t>LOGAN FRANCISCO</t>
   </si>
   <si>
+    <t>CLAUDIA</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
     <t>ZABDIEL</t>
   </si>
   <si>
@@ -296,6 +383,27 @@
     <t>PAUL ADRIAN</t>
   </si>
   <si>
+    <t>DANIEL OCTAVIO</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>GABRIELA DENISSE</t>
+  </si>
+  <si>
+    <t>DANTE GAMALIEL</t>
+  </si>
+  <si>
+    <t>ABDIEL ANTONIO</t>
+  </si>
+  <si>
     <t>MARIA DEL CARMEN</t>
   </si>
   <si>
@@ -303,114 +411,6 @@
   </si>
   <si>
     <t>MELANY NARAYANA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
-  </si>
-  <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>MARILYN</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>DANIEL OCTAVIO</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>GABRIELA DENISSE</t>
-  </si>
-  <si>
-    <t>DANTE GAMALIEL</t>
-  </si>
-  <si>
-    <t>ABDIEL ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -911,7 +911,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -929,7 +929,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -965,7 +965,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -976,7 +976,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -988,13 +988,13 @@
         <v>5</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1006,7 +1006,7 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1030,7 +1030,7 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -1042,7 +1042,7 @@
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1130,7 +1130,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1148,7 +1148,7 @@
         <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -1184,7 +1184,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -1207,7 +1207,7 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -1219,13 +1219,13 @@
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -1237,7 +1237,7 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1261,7 +1261,7 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1515,7 +1515,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -1527,13 +1527,13 @@
         <v>6</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H12">
         <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>8</v>
@@ -1545,7 +1545,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1569,7 +1569,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -1581,7 +1581,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1669,7 +1669,7 @@
         <v>6</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1681,13 +1681,13 @@
         <v>6</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H14">
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>8</v>
@@ -1699,7 +1699,7 @@
         <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1723,7 +1723,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1735,7 +1735,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1823,7 +1823,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -1835,13 +1835,13 @@
         <v>5</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>9</v>
@@ -1853,7 +1853,7 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1877,7 +1877,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1889,7 +1889,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2054,7 +2054,7 @@
         <v>6</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -2066,13 +2066,13 @@
         <v>8</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H19">
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -2084,7 +2084,7 @@
         <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2108,7 +2108,7 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -2120,7 +2120,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2131,7 +2131,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>9</v>
@@ -2143,13 +2143,13 @@
         <v>7</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>6</v>
@@ -2161,7 +2161,7 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2185,7 +2185,7 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2197,7 +2197,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2208,7 +2208,7 @@
         <v>6</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -2220,13 +2220,13 @@
         <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>6</v>
@@ -2238,7 +2238,7 @@
         <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2262,7 +2262,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2274,7 +2274,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2663,7 +2663,7 @@
         <v>6</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H28">
         <v>7</v>
@@ -2681,7 +2681,7 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2717,7 +2717,7 @@
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2740,7 +2740,7 @@
         <v>6</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H29">
         <v>6</v>
@@ -2758,7 +2758,7 @@
         <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2794,7 +2794,7 @@
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2817,7 +2817,7 @@
         <v>5</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H30">
         <v>5</v>
@@ -2835,7 +2835,7 @@
         <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2871,7 +2871,7 @@
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2927,7 +2927,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>48</v>
@@ -2936,30 +2936,30 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>53.85</v>
+        <v>61.54</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>38.46</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>46.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -2968,19 +2968,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>61.54</v>
+        <v>69.23</v>
       </c>
       <c r="G3">
-        <v>38.46</v>
+        <v>30.77</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2991,60 +2991,60 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>67.86</v>
+        <v>69.23</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>30.77</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>32.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
       </c>
       <c r="C5">
+        <v>28</v>
+      </c>
+      <c r="D5">
         <v>26</v>
       </c>
-      <c r="D5">
-        <v>18</v>
-      </c>
       <c r="E5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>69.23</v>
+        <v>92.86</v>
       </c>
       <c r="G5">
-        <v>30.77</v>
+        <v>7.14</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3055,28 +3055,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>92.86</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="G6">
-        <v>7.14</v>
+        <v>3.85</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3087,25 +3087,25 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>96.15000000000001</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="G7">
-        <v>3.85</v>
+        <v>3.57</v>
       </c>
       <c r="H7">
         <v>8</v>
@@ -3124,7 +3124,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3149,426 +3149,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920111</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920112</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920112</v>
-      </c>
-      <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920113</v>
-      </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920115</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920119</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920119</v>
-      </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920120</v>
-      </c>
-      <c r="B10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920120</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920391</v>
-      </c>
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920391</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920125</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920125</v>
-      </c>
-      <c r="B15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920126</v>
-      </c>
-      <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920126</v>
-      </c>
-      <c r="B17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920127</v>
-      </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" t="s">
-        <v>91</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920127</v>
-      </c>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920152</v>
-      </c>
-      <c r="B20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" t="s">
-        <v>92</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920133</v>
-      </c>
-      <c r="B21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920134</v>
-      </c>
-      <c r="B22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -3604,237 +3184,237 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920112</v>
+        <v>21330051920111</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920115</v>
+        <v>21330051920112</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920119</v>
+        <v>21330051920113</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920120</v>
+        <v>21330051920114</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920391</v>
+        <v>21330051920115</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920125</v>
+        <v>21330051920116</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920126</v>
+        <v>21330051920117</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920127</v>
+        <v>21330051920118</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920111</v>
+        <v>21330051920119</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920113</v>
+        <v>20330051920266</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920152</v>
+        <v>21330051920120</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920133</v>
+        <v>21330051920121</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920134</v>
+        <v>21330051920391</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920114</v>
+        <v>21330051920122</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -3842,16 +3422,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920116</v>
+        <v>21330051920123</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -3859,16 +3439,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920117</v>
+        <v>21330051920125</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -3876,16 +3456,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920118</v>
+        <v>21330051920126</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -3893,13 +3473,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920266</v>
+        <v>21330051920127</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
         <v>120</v>
@@ -3910,13 +3490,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920121</v>
-      </c>
-      <c r="B20" t="s">
-        <v>62</v>
+        <v>21330051920129</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
         <v>121</v>
@@ -3927,13 +3504,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920122</v>
+        <v>21330051920130</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
         <v>122</v>
@@ -3944,13 +3521,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920123</v>
+        <v>21330051920131</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
         <v>123</v>
@@ -3961,10 +3538,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920129</v>
+        <v>18330051920377</v>
+      </c>
+      <c r="B23" t="s">
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s">
         <v>124</v>
@@ -3975,13 +3555,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920130</v>
+        <v>21330051920132</v>
       </c>
       <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
         <v>99</v>
-      </c>
-      <c r="C24" t="s">
-        <v>104</v>
       </c>
       <c r="D24" t="s">
         <v>125</v>
@@ -3992,13 +3572,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920131</v>
+        <v>19330051920241</v>
       </c>
       <c r="B25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" t="s">
         <v>100</v>
-      </c>
-      <c r="C25" t="s">
-        <v>112</v>
       </c>
       <c r="D25" t="s">
         <v>126</v>
@@ -4009,13 +3589,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>18330051920377</v>
+        <v>19330051920243</v>
       </c>
       <c r="B26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" t="s">
         <v>101</v>
-      </c>
-      <c r="C26" t="s">
-        <v>113</v>
       </c>
       <c r="D26" t="s">
         <v>127</v>
@@ -4026,13 +3606,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920132</v>
+        <v>20330051920152</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="D27" t="s">
         <v>128</v>
@@ -4043,13 +3623,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920241</v>
+        <v>21330051920133</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
         <v>129</v>
@@ -4060,13 +3640,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920243</v>
+        <v>21330051920134</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
         <v>130</v>
@@ -4082,7 +3662,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4114,45 +3694,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920113</v>
+        <v>21330051920117</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920113</v>
+        <v>21330051920117</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4160,22 +3740,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920117</v>
+        <v>21330051920120</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4183,22 +3763,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920117</v>
+        <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4206,232 +3786,117 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920119</v>
+        <v>21330051920113</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920119</v>
+        <v>21330051920125</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920125</v>
+        <v>21330051920130</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920125</v>
+        <v>18330051920377</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>48</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920126</v>
+        <v>20330051920152</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>50</v>
       </c>
       <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920126</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920111</v>
-      </c>
-      <c r="B12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920130</v>
-      </c>
-      <c r="B13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>18330051920377</v>
-      </c>
-      <c r="B14" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920152</v>
-      </c>
-      <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3APV - Estadisticos 20221.xlsx
+++ b/grupos/3APV - Estadisticos 20221.xlsx
@@ -932,7 +932,7 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -950,7 +950,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>8</v>
@@ -1009,7 +1009,7 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1027,7 +1027,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -1086,7 +1086,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1163,7 +1163,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1181,7 +1181,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1240,7 +1240,7 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1317,7 +1317,7 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1394,7 +1394,7 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1412,7 +1412,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -1471,7 +1471,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1548,7 +1548,7 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1643,7 +1643,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1702,7 +1702,7 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1720,7 +1720,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1779,7 +1779,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1856,7 +1856,7 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1874,7 +1874,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -1933,7 +1933,7 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -1951,7 +1951,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -2010,7 +2010,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2087,7 +2087,7 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2105,7 +2105,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2164,7 +2164,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2182,7 +2182,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2241,7 +2241,7 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2259,7 +2259,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2318,7 +2318,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2336,7 +2336,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>9</v>
@@ -2395,7 +2395,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2472,7 +2472,7 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2490,7 +2490,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2549,7 +2549,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2602,7 +2602,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2631,13 +2631,13 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>9</v>
@@ -2684,7 +2684,7 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2702,7 +2702,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -2838,7 +2838,7 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3044,7 +3044,7 @@
         <v>7.14</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/grupos/3APV - Estadisticos 20221.xlsx
+++ b/grupos/3APV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="131">
   <si>
     <t>Materia</t>
   </si>
@@ -173,13 +173,13 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>Sánchez Sánchez Miguel</t>
+  </si>
+  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
     <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
-    <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
     <t>NC</t>
@@ -935,7 +935,7 @@
         <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -947,13 +947,13 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>7</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -1012,7 +1012,7 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1024,13 +1024,13 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -1089,7 +1089,7 @@
         <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1101,7 +1101,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1119,7 +1119,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1166,7 +1166,7 @@
         <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1178,7 +1178,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -1196,7 +1196,7 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1243,7 +1243,7 @@
         <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1255,7 +1255,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -1320,7 +1320,7 @@
         <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1332,7 +1332,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1409,7 +1409,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
         <v>6</v>
@@ -1427,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1474,7 +1474,7 @@
         <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1486,7 +1486,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1551,7 +1551,7 @@
         <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1563,7 +1563,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1581,7 +1581,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1628,7 +1628,7 @@
         <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1640,7 +1640,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1658,7 +1658,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1705,7 +1705,7 @@
         <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1717,7 +1717,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>6</v>
@@ -1735,7 +1735,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1782,7 +1782,7 @@
         <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1794,13 +1794,13 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>10</v>
@@ -1859,7 +1859,7 @@
         <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1871,13 +1871,13 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>6</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1889,7 +1889,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1936,7 +1936,7 @@
         <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -2013,7 +2013,7 @@
         <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2025,7 +2025,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -2043,7 +2043,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2090,7 +2090,7 @@
         <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2102,13 +2102,13 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>6</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -2120,7 +2120,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2167,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2179,13 +2179,13 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>6</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2244,7 +2244,7 @@
         <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2256,13 +2256,13 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>6</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2321,7 +2321,7 @@
         <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2333,13 +2333,13 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>6</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2351,7 +2351,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2398,7 +2398,7 @@
         <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2410,7 +2410,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2428,7 +2428,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2475,7 +2475,7 @@
         <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2487,7 +2487,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2552,7 +2552,7 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2564,7 +2564,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2605,7 +2605,7 @@
         <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2634,13 +2634,13 @@
         <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>7</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2687,7 +2687,7 @@
         <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2699,7 +2699,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>6</v>
@@ -2764,7 +2764,7 @@
         <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -2776,7 +2776,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>6</v>
@@ -2841,7 +2841,7 @@
         <v>5</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -2853,13 +2853,13 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
         <v>5</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V30">
         <v>8</v>
@@ -3000,19 +3000,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>69.23</v>
+        <v>73.08</v>
       </c>
       <c r="G4">
-        <v>30.77</v>
+        <v>26.92</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -3044,7 +3044,7 @@
         <v>7.14</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3055,28 +3055,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="C6">
+        <v>28</v>
+      </c>
+      <c r="D6">
         <v>26</v>
       </c>
-      <c r="D6">
-        <v>25</v>
-      </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>96.15000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="G6">
-        <v>3.85</v>
+        <v>7.14</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3087,25 +3087,25 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>96.43000000000001</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="G7">
-        <v>3.57</v>
+        <v>3.85</v>
       </c>
       <c r="H7">
         <v>8</v>
@@ -3662,7 +3662,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3786,16 +3786,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920113</v>
+        <v>21330051920391</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -3809,22 +3809,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920125</v>
+        <v>21330051920391</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3832,22 +3832,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920130</v>
+        <v>21330051920113</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3855,22 +3855,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>18330051920377</v>
+        <v>21330051920125</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -3878,24 +3878,70 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
+        <v>21330051920130</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>18330051920377</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
         <v>20330051920152</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" t="s">
         <v>79</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C12" t="s">
         <v>59</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D12" t="s">
         <v>128</v>
       </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
         <v>50</v>
       </c>
-      <c r="G10">
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APV - Estadisticos 20221.xlsx
+++ b/grupos/3APV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="131">
   <si>
     <t>Materia</t>
   </si>
@@ -167,10 +167,10 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
     <t>Sánchez Sánchez Miguel</t>
@@ -938,10 +938,10 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -959,7 +959,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -1015,10 +1015,10 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1033,7 +1033,7 @@
         <v>6</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>5</v>
@@ -1092,10 +1092,10 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1169,10 +1169,10 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1187,10 +1187,10 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1246,10 +1246,10 @@
         <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1323,10 +1323,10 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1400,10 +1400,10 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1421,7 +1421,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -1477,10 +1477,10 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1554,10 +1554,10 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1575,7 +1575,7 @@
         <v>7</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1631,10 +1631,10 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1649,7 +1649,7 @@
         <v>7</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1708,10 +1708,10 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1729,7 +1729,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1785,10 +1785,10 @@
         <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1806,7 +1806,7 @@
         <v>10</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1862,10 +1862,10 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1939,10 +1939,10 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -1957,7 +1957,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2016,10 +2016,10 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2093,10 +2093,10 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2111,10 +2111,10 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2170,10 +2170,10 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2188,10 +2188,10 @@
         <v>6</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2247,10 +2247,10 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2324,10 +2324,10 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2401,10 +2401,10 @@
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2478,10 +2478,10 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2555,10 +2555,10 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2690,10 +2690,10 @@
         <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2708,7 +2708,7 @@
         <v>8</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2767,10 +2767,10 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -2788,7 +2788,7 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>5</v>
@@ -2844,10 +2844,10 @@
         <v>4</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -2862,10 +2862,10 @@
         <v>5</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X30">
         <v>5</v>
@@ -2959,7 +2959,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -2968,19 +2968,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>69.23</v>
+        <v>73.08</v>
       </c>
       <c r="G3">
-        <v>30.77</v>
+        <v>26.92</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -3000,19 +3000,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>73.08</v>
+        <v>80.77</v>
       </c>
       <c r="G4">
-        <v>26.92</v>
+        <v>19.23</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3662,7 +3662,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3694,22 +3694,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920117</v>
+        <v>21330051920391</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3717,16 +3717,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920117</v>
+        <v>21330051920391</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -3740,22 +3740,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920120</v>
+        <v>21330051920133</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920120</v>
+        <v>21330051920133</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3786,22 +3786,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920391</v>
+        <v>21330051920117</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3809,16 +3809,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920391</v>
+        <v>21330051920120</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -3832,19 +3832,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920113</v>
+        <v>21330051920125</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>49</v>
@@ -3855,22 +3855,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920125</v>
+        <v>21330051920130</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -3878,16 +3878,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920130</v>
+        <v>18330051920377</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -3901,47 +3901,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>18330051920377</v>
+        <v>20330051920152</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920152</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" t="s">
-        <v>128</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APV - Estadisticos 20221.xlsx
+++ b/grupos/3APV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="131">
   <si>
     <t>Materia</t>
   </si>
@@ -164,13 +164,13 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
     <t>Sánchez Sánchez Miguel</t>
@@ -944,7 +944,7 @@
         <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>8</v>
@@ -962,7 +962,7 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -1021,7 +1021,7 @@
         <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
         <v>5</v>
@@ -1039,7 +1039,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1098,7 +1098,7 @@
         <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>6</v>
@@ -1175,7 +1175,7 @@
         <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>6</v>
@@ -1252,7 +1252,7 @@
         <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
         <v>5</v>
@@ -1329,7 +1329,7 @@
         <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>10</v>
@@ -1406,7 +1406,7 @@
         <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>6</v>
@@ -1424,7 +1424,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1483,7 +1483,7 @@
         <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>10</v>
@@ -1560,7 +1560,7 @@
         <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>6</v>
@@ -1637,7 +1637,7 @@
         <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>8</v>
@@ -1714,7 +1714,7 @@
         <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>6</v>
@@ -1732,7 +1732,7 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1791,7 +1791,7 @@
         <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>10</v>
@@ -1868,7 +1868,7 @@
         <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>8</v>
@@ -1886,7 +1886,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -1945,7 +1945,7 @@
         <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>8</v>
@@ -2022,7 +2022,7 @@
         <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>9</v>
@@ -2099,7 +2099,7 @@
         <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>5</v>
@@ -2117,7 +2117,7 @@
         <v>6</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2176,7 +2176,7 @@
         <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>5</v>
@@ -2253,7 +2253,7 @@
         <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>5</v>
@@ -2271,7 +2271,7 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2330,7 +2330,7 @@
         <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>6</v>
@@ -2348,7 +2348,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2407,7 +2407,7 @@
         <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>8</v>
@@ -2484,7 +2484,7 @@
         <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>7</v>
@@ -2502,7 +2502,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2561,7 +2561,7 @@
         <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>10</v>
@@ -2696,7 +2696,7 @@
         <v>6</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
         <v>5</v>
@@ -2773,7 +2773,7 @@
         <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
         <v>5</v>
@@ -2791,7 +2791,7 @@
         <v>6</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -2850,7 +2850,7 @@
         <v>5</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>5</v>
@@ -2927,7 +2927,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>48</v>
@@ -2936,19 +2936,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>61.54</v>
+        <v>73.08</v>
       </c>
       <c r="G2">
-        <v>38.46</v>
+        <v>26.92</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2959,7 +2959,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -2968,19 +2968,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>73.08</v>
+        <v>80.77</v>
       </c>
       <c r="G3">
-        <v>26.92</v>
+        <v>19.23</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -3000,16 +3000,16 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>80.77</v>
+        <v>92.31</v>
       </c>
       <c r="G4">
-        <v>19.23</v>
+        <v>7.69</v>
       </c>
       <c r="H4">
         <v>6.9</v>
@@ -3662,7 +3662,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3694,22 +3694,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920391</v>
+        <v>21330051920112</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3717,19 +3717,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920391</v>
+        <v>21330051920112</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>48</v>
@@ -3740,22 +3740,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920133</v>
+        <v>21330051920127</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920133</v>
+        <v>21330051920127</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3786,22 +3786,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920117</v>
+        <v>21330051920391</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3809,19 +3809,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920120</v>
+        <v>21330051920125</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>48</v>
@@ -3832,22 +3832,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920125</v>
+        <v>20330051920152</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3855,70 +3855,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920130</v>
+        <v>21330051920133</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>48</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>18330051920377</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" t="s">
-        <v>124</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920152</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>
